--- a/Carte de saturation par thème.xlsx
+++ b/Carte de saturation par thème.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uqtrsspt-my.sharepoint.com/personal/amour_joel_ombassa_uqtr_ca/Documents/AMOUR JOEL/Projet de thèse de doctorat - Ombassa/Articles à soumettre/Invitation au Colloque à Abidjan et bille d'avion/Feedback des éditeurs au 28 mai 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5DAB7038-32BF-4194-AB16-DFF7F09D9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAAD8CD9-C230-4D63-9013-AE06CDC7B36D}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5DAB7038-32BF-4194-AB16-DFF7F09D9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B521CA1A-743C-4088-B070-5B45A5785115}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FE8C386-3AC7-48FE-9A3A-6D2FF06F8EBC}"/>
   </bookViews>
@@ -410,9 +410,6 @@
     <t>SYNTHÈSE DE SATURATION — AXES ANALYTIQUES POUR L'ARTICLE</t>
   </si>
   <si>
-    <t>Sur la base de la carte de saturation, trois niveaux de thèmes se dégagent pour structurer l'article :</t>
-  </si>
-  <si>
     <t>Niveau</t>
   </si>
   <si>
@@ -465,6 +462,9 @@
   </si>
   <si>
     <t>CARTE DE SATURATION THÉMATIQUE - OMBASSA, AMOUR JOEL</t>
+  </si>
+  <si>
+    <t>Sur la base de la carte de saturation, quatre niveaux de thèmes se dégagent pour structurer l'article :</t>
   </si>
 </sst>
 </file>
@@ -911,6 +911,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1251,7 +1255,7 @@
   <sheetData>
     <row r="2" spans="2:13" ht="24" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -3204,21 +3208,21 @@
     </row>
     <row r="63" spans="2:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="25" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="2:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="D64" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="E64" s="27" t="s">
         <v>126</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="33" thickBot="1" x14ac:dyDescent="0.3">
@@ -3226,13 +3230,13 @@
         <v>19</v>
       </c>
       <c r="C65" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D65" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D65" s="29" t="s">
-        <v>129</v>
-      </c>
       <c r="E65" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -3240,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="C66" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="31" t="s">
-        <v>131</v>
-      </c>
       <c r="E66" s="31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -3254,13 +3258,13 @@
         <v>37</v>
       </c>
       <c r="C67" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D67" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D67" s="33" t="s">
-        <v>133</v>
-      </c>
       <c r="E67" s="33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.3">
@@ -3268,18 +3272,18 @@
         <v>49</v>
       </c>
       <c r="C68" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="35" t="s">
-        <v>135</v>
-      </c>
       <c r="E68" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Carte de saturation par thème.xlsx
+++ b/Carte de saturation par thème.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uqtrsspt-my.sharepoint.com/personal/amour_joel_ombassa_uqtr_ca/Documents/AMOUR JOEL/Projet de thèse de doctorat - Ombassa/Articles à soumettre/Invitation au Colloque à Abidjan et bille d'avion/Feedback des éditeurs au 28 mai 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5DAB7038-32BF-4194-AB16-DFF7F09D9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B521CA1A-743C-4088-B070-5B45A5785115}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{5DAB7038-32BF-4194-AB16-DFF7F09D9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BB3D406-4474-4970-9BEA-7FC9E07225E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FE8C386-3AC7-48FE-9A3A-6D2FF06F8EBC}"/>
   </bookViews>
@@ -464,7 +464,7 @@
     <t>CARTE DE SATURATION THÉMATIQUE - OMBASSA, AMOUR JOEL</t>
   </si>
   <si>
-    <t>Sur la base de la carte de saturation, quatre niveaux de thèmes se dégagent pour structurer l'article :</t>
+    <t>Sur la base de la carte de saturation, quatre niveaux de thèmes se dégagent pour structurer notre article :</t>
   </si>
 </sst>
 </file>
